--- a/data_lake/bart_temp_med/dt=2026-08-07/temperaturamed.xlsx
+++ b/data_lake/bart_temp_med/dt=2026-08-07/temperaturamed.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\01. Tematicas\05. Datos Hidrometeorologicos\01. Productos\02.Tablas\temporales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E66B64E2-D17D-4469-B5F8-405C3A202DD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{855F8525-0F58-4A3A-9414-50E5D92F4EBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="729" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,6 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DHIME!$A$1:$S$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Temperatura!$P$1:$P$212</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Temperatura!$B$4:$R$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -6353,8 +6354,8 @@
     <col min="43" max="43" width="20.7109375" style="53" customWidth="1"/>
     <col min="44" max="44" width="24.85546875" style="69" customWidth="1"/>
     <col min="45" max="45" width="13.28515625" style="70" bestFit="1" customWidth="1"/>
-    <col min="46" max="124" width="32.42578125" style="50" customWidth="1"/>
-    <col min="125" max="16384" width="32.42578125" style="50"/>
+    <col min="46" max="125" width="32.42578125" style="50" customWidth="1"/>
+    <col min="126" max="16384" width="32.42578125" style="50"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.2">
@@ -6652,7 +6653,9 @@
       <c r="O5" s="56">
         <v>29.4</v>
       </c>
-      <c r="P5" s="56"/>
+      <c r="P5" s="56">
+        <v>29.6</v>
+      </c>
       <c r="Q5" s="56"/>
       <c r="R5" s="56"/>
       <c r="S5" s="56"/>
@@ -6680,7 +6683,7 @@
       <c r="AO5" s="56"/>
       <c r="AP5" s="58">
         <f t="shared" ref="AP5:AP68" si="0">COUNTIF(K5:AO5,"&gt;0")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ5" s="71" t="str">
         <f t="shared" ref="AQ5:AQ68" si="1">IF(AP5&gt;14,AVERAGE(K5:AO5),"")</f>
@@ -6741,7 +6744,9 @@
       <c r="O6" s="56">
         <v>29.5</v>
       </c>
-      <c r="P6" s="56"/>
+      <c r="P6" s="56">
+        <v>29.3</v>
+      </c>
       <c r="Q6" s="56"/>
       <c r="R6" s="56"/>
       <c r="S6" s="56"/>
@@ -6769,7 +6774,7 @@
       <c r="AO6" s="56"/>
       <c r="AP6" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ6" s="71" t="str">
         <f t="shared" si="1"/>
@@ -6830,7 +6835,9 @@
       <c r="O7" s="56">
         <v>31</v>
       </c>
-      <c r="P7" s="56"/>
+      <c r="P7" s="56">
+        <v>30.1</v>
+      </c>
       <c r="Q7" s="56"/>
       <c r="R7" s="56"/>
       <c r="S7" s="56"/>
@@ -6858,7 +6865,7 @@
       <c r="AO7" s="56"/>
       <c r="AP7" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ7" s="71" t="str">
         <f t="shared" si="1"/>
@@ -6919,7 +6926,9 @@
       <c r="O8" s="56">
         <v>29.8</v>
       </c>
-      <c r="P8" s="56"/>
+      <c r="P8" s="56">
+        <v>29</v>
+      </c>
       <c r="Q8" s="56"/>
       <c r="R8" s="56"/>
       <c r="S8" s="56"/>
@@ -6947,7 +6956,7 @@
       <c r="AO8" s="56"/>
       <c r="AP8" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ8" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7008,7 +7017,9 @@
       <c r="O9" s="56">
         <v>29.7</v>
       </c>
-      <c r="P9" s="56"/>
+      <c r="P9" s="56">
+        <v>29.5</v>
+      </c>
       <c r="Q9" s="56"/>
       <c r="R9" s="56"/>
       <c r="S9" s="56"/>
@@ -7036,7 +7047,7 @@
       <c r="AO9" s="56"/>
       <c r="AP9" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ9" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7095,9 +7106,11 @@
         <v>33</v>
       </c>
       <c r="O10" s="56">
-        <v>28</v>
-      </c>
-      <c r="P10" s="56"/>
+        <v>31.3</v>
+      </c>
+      <c r="P10" s="56">
+        <v>32</v>
+      </c>
       <c r="Q10" s="56"/>
       <c r="R10" s="56"/>
       <c r="S10" s="56"/>
@@ -7125,7 +7138,7 @@
       <c r="AO10" s="56"/>
       <c r="AP10" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ10" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7186,7 +7199,9 @@
       <c r="O11" s="56">
         <v>32.9</v>
       </c>
-      <c r="P11" s="56"/>
+      <c r="P11" s="56">
+        <v>31.2</v>
+      </c>
       <c r="Q11" s="56"/>
       <c r="R11" s="56"/>
       <c r="S11" s="56"/>
@@ -7214,7 +7229,7 @@
       <c r="AO11" s="56"/>
       <c r="AP11" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ11" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7275,7 +7290,9 @@
       <c r="O12" s="56">
         <v>30.7</v>
       </c>
-      <c r="P12" s="56"/>
+      <c r="P12" s="56">
+        <v>25.4</v>
+      </c>
       <c r="Q12" s="56"/>
       <c r="R12" s="56"/>
       <c r="S12" s="56"/>
@@ -7303,7 +7320,7 @@
       <c r="AO12" s="56"/>
       <c r="AP12" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ12" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7364,7 +7381,9 @@
       <c r="O13" s="56">
         <v>30.8</v>
       </c>
-      <c r="P13" s="56"/>
+      <c r="P13" s="56">
+        <v>29.1</v>
+      </c>
       <c r="Q13" s="56"/>
       <c r="R13" s="56"/>
       <c r="S13" s="56"/>
@@ -7392,7 +7411,7 @@
       <c r="AO13" s="56"/>
       <c r="AP13" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ13" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7453,7 +7472,9 @@
       <c r="O14" s="56">
         <v>24</v>
       </c>
-      <c r="P14" s="56"/>
+      <c r="P14" s="56">
+        <v>21.4</v>
+      </c>
       <c r="Q14" s="56"/>
       <c r="R14" s="56"/>
       <c r="S14" s="56"/>
@@ -7481,7 +7502,7 @@
       <c r="AO14" s="56"/>
       <c r="AP14" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ14" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7542,7 +7563,9 @@
       <c r="O15" s="56">
         <v>30.8</v>
       </c>
-      <c r="P15" s="56"/>
+      <c r="P15" s="56">
+        <v>29.8</v>
+      </c>
       <c r="Q15" s="56"/>
       <c r="R15" s="56"/>
       <c r="S15" s="56"/>
@@ -7570,7 +7593,7 @@
       <c r="AO15" s="56"/>
       <c r="AP15" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ15" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7631,7 +7654,9 @@
       <c r="O16" s="56">
         <v>27.3</v>
       </c>
-      <c r="P16" s="56"/>
+      <c r="P16" s="56">
+        <v>25.2</v>
+      </c>
       <c r="Q16" s="56"/>
       <c r="R16" s="56"/>
       <c r="S16" s="56"/>
@@ -7659,7 +7684,7 @@
       <c r="AO16" s="56"/>
       <c r="AP16" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ16" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7720,7 +7745,9 @@
       <c r="O17" s="56">
         <v>25.1</v>
       </c>
-      <c r="P17" s="56"/>
+      <c r="P17" s="56">
+        <v>25.1</v>
+      </c>
       <c r="Q17" s="56"/>
       <c r="R17" s="56"/>
       <c r="S17" s="56"/>
@@ -7748,7 +7775,7 @@
       <c r="AO17" s="56"/>
       <c r="AP17" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ17" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7809,7 +7836,9 @@
       <c r="O18" s="56">
         <v>19.2</v>
       </c>
-      <c r="P18" s="56"/>
+      <c r="P18" s="56">
+        <v>19.3</v>
+      </c>
       <c r="Q18" s="56"/>
       <c r="R18" s="56"/>
       <c r="S18" s="56"/>
@@ -7837,7 +7866,7 @@
       <c r="AO18" s="56"/>
       <c r="AP18" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ18" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7898,7 +7927,9 @@
       <c r="O19" s="56">
         <v>22.3</v>
       </c>
-      <c r="P19" s="56"/>
+      <c r="P19" s="56">
+        <v>24</v>
+      </c>
       <c r="Q19" s="56"/>
       <c r="R19" s="56"/>
       <c r="S19" s="56"/>
@@ -7926,7 +7957,7 @@
       <c r="AO19" s="56"/>
       <c r="AP19" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ19" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7987,7 +8018,9 @@
       <c r="O20" s="56">
         <v>23.9</v>
       </c>
-      <c r="P20" s="56"/>
+      <c r="P20" s="56">
+        <v>23.5</v>
+      </c>
       <c r="Q20" s="56"/>
       <c r="R20" s="56"/>
       <c r="S20" s="56"/>
@@ -8015,7 +8048,7 @@
       <c r="AO20" s="56"/>
       <c r="AP20" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ20" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8076,7 +8109,9 @@
       <c r="O21" s="56">
         <v>26.4</v>
       </c>
-      <c r="P21" s="56"/>
+      <c r="P21" s="56">
+        <v>29.2</v>
+      </c>
       <c r="Q21" s="56"/>
       <c r="R21" s="56"/>
       <c r="S21" s="56"/>
@@ -8104,7 +8139,7 @@
       <c r="AO21" s="56"/>
       <c r="AP21" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ21" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8165,7 +8200,9 @@
       <c r="O22" s="56">
         <v>14.6</v>
       </c>
-      <c r="P22" s="56"/>
+      <c r="P22" s="56">
+        <v>14.8</v>
+      </c>
       <c r="Q22" s="56"/>
       <c r="R22" s="56"/>
       <c r="S22" s="56"/>
@@ -8193,7 +8230,7 @@
       <c r="AO22" s="56"/>
       <c r="AP22" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ22" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8254,7 +8291,9 @@
       <c r="O23" s="56">
         <v>25.4</v>
       </c>
-      <c r="P23" s="56"/>
+      <c r="P23" s="56">
+        <v>25.9</v>
+      </c>
       <c r="Q23" s="56"/>
       <c r="R23" s="56"/>
       <c r="S23" s="56"/>
@@ -8282,7 +8321,7 @@
       <c r="AO23" s="56"/>
       <c r="AP23" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ23" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8343,7 +8382,9 @@
       <c r="O24" s="56">
         <v>27.9</v>
       </c>
-      <c r="P24" s="56"/>
+      <c r="P24" s="56">
+        <v>30.8</v>
+      </c>
       <c r="Q24" s="56"/>
       <c r="R24" s="56"/>
       <c r="S24" s="56"/>
@@ -8371,7 +8412,7 @@
       <c r="AO24" s="56"/>
       <c r="AP24" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ24" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8432,7 +8473,9 @@
       <c r="O25" s="56">
         <v>21.4</v>
       </c>
-      <c r="P25" s="56"/>
+      <c r="P25" s="56">
+        <v>21.4</v>
+      </c>
       <c r="Q25" s="56"/>
       <c r="R25" s="56"/>
       <c r="S25" s="56"/>
@@ -8460,7 +8503,7 @@
       <c r="AO25" s="56"/>
       <c r="AP25" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ25" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8521,7 +8564,9 @@
       <c r="O26" s="56">
         <v>10.3</v>
       </c>
-      <c r="P26" s="56"/>
+      <c r="P26" s="56">
+        <v>11.4</v>
+      </c>
       <c r="Q26" s="56"/>
       <c r="R26" s="56"/>
       <c r="S26" s="56"/>
@@ -8549,7 +8594,7 @@
       <c r="AO26" s="56"/>
       <c r="AP26" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ26" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8610,7 +8655,9 @@
       <c r="O27" s="56">
         <v>26.5</v>
       </c>
-      <c r="P27" s="56"/>
+      <c r="P27" s="56">
+        <v>26</v>
+      </c>
       <c r="Q27" s="56"/>
       <c r="R27" s="56"/>
       <c r="S27" s="56"/>
@@ -8638,7 +8685,7 @@
       <c r="AO27" s="56"/>
       <c r="AP27" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ27" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8699,7 +8746,9 @@
       <c r="O28" s="56">
         <v>27.8</v>
       </c>
-      <c r="P28" s="56"/>
+      <c r="P28" s="56">
+        <v>27.4</v>
+      </c>
       <c r="Q28" s="56"/>
       <c r="R28" s="56"/>
       <c r="S28" s="56"/>
@@ -8727,7 +8776,7 @@
       <c r="AO28" s="56"/>
       <c r="AP28" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ28" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8788,7 +8837,9 @@
       <c r="O29" s="56">
         <v>27</v>
       </c>
-      <c r="P29" s="56"/>
+      <c r="P29" s="56">
+        <v>27.3</v>
+      </c>
       <c r="Q29" s="56"/>
       <c r="R29" s="56"/>
       <c r="S29" s="56"/>
@@ -8816,7 +8867,7 @@
       <c r="AO29" s="56"/>
       <c r="AP29" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ29" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8877,7 +8928,9 @@
       <c r="O30" s="56">
         <v>23.2</v>
       </c>
-      <c r="P30" s="56"/>
+      <c r="P30" s="56">
+        <v>26.1</v>
+      </c>
       <c r="Q30" s="56"/>
       <c r="R30" s="56"/>
       <c r="S30" s="56"/>
@@ -8905,7 +8958,7 @@
       <c r="AO30" s="56"/>
       <c r="AP30" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ30" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8966,7 +9019,9 @@
       <c r="O31" s="98">
         <v>28.6</v>
       </c>
-      <c r="P31" s="98"/>
+      <c r="P31" s="98">
+        <v>27.6</v>
+      </c>
       <c r="Q31" s="98"/>
       <c r="R31" s="98"/>
       <c r="S31" s="98"/>
@@ -8994,7 +9049,7 @@
       <c r="AO31" s="98"/>
       <c r="AP31" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ31" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9055,7 +9110,9 @@
       <c r="O32" s="56">
         <v>17.8</v>
       </c>
-      <c r="P32" s="56"/>
+      <c r="P32" s="56">
+        <v>20.6</v>
+      </c>
       <c r="Q32" s="56"/>
       <c r="R32" s="56"/>
       <c r="S32" s="56"/>
@@ -9083,7 +9140,7 @@
       <c r="AO32" s="56"/>
       <c r="AP32" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ32" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9144,7 +9201,9 @@
       <c r="O33" s="56">
         <v>27.15</v>
       </c>
-      <c r="P33" s="56"/>
+      <c r="P33" s="56">
+        <v>25.1</v>
+      </c>
       <c r="Q33" s="56"/>
       <c r="R33" s="56"/>
       <c r="S33" s="56"/>
@@ -9172,7 +9231,7 @@
       <c r="AO33" s="56"/>
       <c r="AP33" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ33" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9233,7 +9292,9 @@
       <c r="O34" s="56">
         <v>20.266666666666669</v>
       </c>
-      <c r="P34" s="56"/>
+      <c r="P34" s="56">
+        <v>20.666666666666671</v>
+      </c>
       <c r="Q34" s="56"/>
       <c r="R34" s="56"/>
       <c r="S34" s="56"/>
@@ -9261,7 +9322,7 @@
       <c r="AO34" s="56"/>
       <c r="AP34" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ34" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9322,7 +9383,9 @@
       <c r="O35" s="56">
         <v>23.6</v>
       </c>
-      <c r="P35" s="56"/>
+      <c r="P35" s="56">
+        <v>25</v>
+      </c>
       <c r="Q35" s="56"/>
       <c r="R35" s="56"/>
       <c r="S35" s="56"/>
@@ -9350,7 +9413,7 @@
       <c r="AO35" s="56"/>
       <c r="AP35" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ35" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9411,7 +9474,9 @@
       <c r="O36" s="56">
         <v>19.100000000000001</v>
       </c>
-      <c r="P36" s="56"/>
+      <c r="P36" s="56">
+        <v>19.3</v>
+      </c>
       <c r="Q36" s="56"/>
       <c r="R36" s="56"/>
       <c r="S36" s="56"/>
@@ -9439,7 +9504,7 @@
       <c r="AO36" s="56"/>
       <c r="AP36" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ36" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9500,7 +9565,9 @@
       <c r="O37" s="56">
         <v>27.25</v>
       </c>
-      <c r="P37" s="56"/>
+      <c r="P37" s="56">
+        <v>27.05</v>
+      </c>
       <c r="Q37" s="56"/>
       <c r="R37" s="56"/>
       <c r="S37" s="56"/>
@@ -9528,7 +9595,7 @@
       <c r="AO37" s="56"/>
       <c r="AP37" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ37" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9589,7 +9656,9 @@
       <c r="O38" s="56">
         <v>16</v>
       </c>
-      <c r="P38" s="56"/>
+      <c r="P38" s="56">
+        <v>16.350000000000001</v>
+      </c>
       <c r="Q38" s="56"/>
       <c r="R38" s="56"/>
       <c r="S38" s="56"/>
@@ -9617,7 +9686,7 @@
       <c r="AO38" s="56"/>
       <c r="AP38" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ38" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9678,7 +9747,9 @@
       <c r="O39" s="56">
         <v>22.86666666666666</v>
       </c>
-      <c r="P39" s="56"/>
+      <c r="P39" s="56">
+        <v>21.4</v>
+      </c>
       <c r="Q39" s="56"/>
       <c r="R39" s="56"/>
       <c r="S39" s="56"/>
@@ -9706,7 +9777,7 @@
       <c r="AO39" s="56"/>
       <c r="AP39" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ39" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9763,7 +9834,9 @@
         <v>25.8</v>
       </c>
       <c r="O40" s="56"/>
-      <c r="P40" s="56"/>
+      <c r="P40" s="56">
+        <v>25</v>
+      </c>
       <c r="Q40" s="56"/>
       <c r="R40" s="56"/>
       <c r="S40" s="56"/>
@@ -9791,7 +9864,7 @@
       <c r="AO40" s="56"/>
       <c r="AP40" s="58">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ40" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9852,7 +9925,9 @@
       <c r="O41" s="56">
         <v>19.06666666666667</v>
       </c>
-      <c r="P41" s="56"/>
+      <c r="P41" s="56">
+        <v>20.466666666666669</v>
+      </c>
       <c r="Q41" s="56"/>
       <c r="R41" s="56"/>
       <c r="S41" s="56"/>
@@ -9880,7 +9955,7 @@
       <c r="AO41" s="56"/>
       <c r="AP41" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ41" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9941,7 +10016,9 @@
       <c r="O42" s="56">
         <v>28.3</v>
       </c>
-      <c r="P42" s="56"/>
+      <c r="P42" s="56">
+        <v>24.1</v>
+      </c>
       <c r="Q42" s="56"/>
       <c r="R42" s="56"/>
       <c r="S42" s="56"/>
@@ -9969,7 +10046,7 @@
       <c r="AO42" s="56"/>
       <c r="AP42" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ42" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10030,7 +10107,9 @@
       <c r="O43" s="56">
         <v>29.8</v>
       </c>
-      <c r="P43" s="56"/>
+      <c r="P43" s="56">
+        <v>25.65</v>
+      </c>
       <c r="Q43" s="56"/>
       <c r="R43" s="56"/>
       <c r="S43" s="56"/>
@@ -10058,7 +10137,7 @@
       <c r="AO43" s="56"/>
       <c r="AP43" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ43" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10119,7 +10198,9 @@
       <c r="O44" s="56">
         <v>27.65</v>
       </c>
-      <c r="P44" s="56"/>
+      <c r="P44" s="56">
+        <v>26.8</v>
+      </c>
       <c r="Q44" s="56"/>
       <c r="R44" s="56"/>
       <c r="S44" s="56"/>
@@ -10147,7 +10228,7 @@
       <c r="AO44" s="56"/>
       <c r="AP44" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ44" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10208,7 +10289,9 @@
       <c r="O45" s="56">
         <v>29.4</v>
       </c>
-      <c r="P45" s="56"/>
+      <c r="P45" s="56">
+        <v>25.35</v>
+      </c>
       <c r="Q45" s="56"/>
       <c r="R45" s="56"/>
       <c r="S45" s="56"/>
@@ -10236,7 +10319,7 @@
       <c r="AO45" s="56"/>
       <c r="AP45" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ45" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10297,7 +10380,9 @@
       <c r="O46" s="56">
         <v>28.95</v>
       </c>
-      <c r="P46" s="56"/>
+      <c r="P46" s="56">
+        <v>26.2</v>
+      </c>
       <c r="Q46" s="56"/>
       <c r="R46" s="56"/>
       <c r="S46" s="56"/>
@@ -10325,7 +10410,7 @@
       <c r="AO46" s="56"/>
       <c r="AP46" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ46" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10386,7 +10471,9 @@
       <c r="O47" s="56">
         <v>30.666666666666671</v>
       </c>
-      <c r="P47" s="56"/>
+      <c r="P47" s="56">
+        <v>25.533333333333331</v>
+      </c>
       <c r="Q47" s="56"/>
       <c r="R47" s="56"/>
       <c r="S47" s="56"/>
@@ -10414,7 +10501,7 @@
       <c r="AO47" s="56"/>
       <c r="AP47" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ47" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10633,7 +10720,9 @@
       <c r="O50" s="56">
         <v>28.05</v>
       </c>
-      <c r="P50" s="56"/>
+      <c r="P50" s="56">
+        <v>26.55</v>
+      </c>
       <c r="Q50" s="56"/>
       <c r="R50" s="56"/>
       <c r="S50" s="56"/>
@@ -10661,7 +10750,7 @@
       <c r="AO50" s="56"/>
       <c r="AP50" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ50" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10880,7 +10969,9 @@
       <c r="O53" s="56">
         <v>29.05</v>
       </c>
-      <c r="P53" s="56"/>
+      <c r="P53" s="56">
+        <v>25.2</v>
+      </c>
       <c r="Q53" s="56"/>
       <c r="R53" s="56"/>
       <c r="S53" s="56"/>
@@ -10908,7 +10999,7 @@
       <c r="AO53" s="56"/>
       <c r="AP53" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ53" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10966,8 +11057,12 @@
       <c r="N54" s="56">
         <v>28.8</v>
       </c>
-      <c r="O54" s="56"/>
-      <c r="P54" s="56"/>
+      <c r="O54" s="56">
+        <v>30.1</v>
+      </c>
+      <c r="P54" s="56">
+        <v>25.9</v>
+      </c>
       <c r="Q54" s="56"/>
       <c r="R54" s="56"/>
       <c r="S54" s="56"/>
@@ -10995,7 +11090,7 @@
       <c r="AO54" s="56"/>
       <c r="AP54" s="58">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AQ54" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11056,7 +11151,9 @@
       <c r="O55" s="56">
         <v>30.75</v>
       </c>
-      <c r="P55" s="56"/>
+      <c r="P55" s="56">
+        <v>28.05</v>
+      </c>
       <c r="Q55" s="56"/>
       <c r="R55" s="56"/>
       <c r="S55" s="56"/>
@@ -11084,7 +11181,7 @@
       <c r="AO55" s="56"/>
       <c r="AP55" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ55" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11145,7 +11242,9 @@
       <c r="O56" s="56">
         <v>30.25</v>
       </c>
-      <c r="P56" s="56"/>
+      <c r="P56" s="56">
+        <v>29.3</v>
+      </c>
       <c r="Q56" s="56"/>
       <c r="R56" s="56"/>
       <c r="S56" s="56"/>
@@ -11173,7 +11272,7 @@
       <c r="AO56" s="56"/>
       <c r="AP56" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ56" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11392,7 +11491,9 @@
       <c r="O59" s="56">
         <v>29.4</v>
       </c>
-      <c r="P59" s="56"/>
+      <c r="P59" s="56">
+        <v>25.45</v>
+      </c>
       <c r="Q59" s="56"/>
       <c r="R59" s="56"/>
       <c r="S59" s="56"/>
@@ -11420,7 +11521,7 @@
       <c r="AO59" s="56"/>
       <c r="AP59" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ59" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11560,7 +11661,9 @@
       <c r="O61" s="56">
         <v>27.1</v>
       </c>
-      <c r="P61" s="56"/>
+      <c r="P61" s="56">
+        <v>27.95</v>
+      </c>
       <c r="Q61" s="56"/>
       <c r="R61" s="56"/>
       <c r="S61" s="56"/>
@@ -11588,7 +11691,7 @@
       <c r="AO61" s="56"/>
       <c r="AP61" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ61" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11649,7 +11752,9 @@
       <c r="O62" s="56">
         <v>25.93333333333333</v>
       </c>
-      <c r="P62" s="56"/>
+      <c r="P62" s="56">
+        <v>27.733333333333331</v>
+      </c>
       <c r="Q62" s="56"/>
       <c r="R62" s="56"/>
       <c r="S62" s="56"/>
@@ -11677,7 +11782,7 @@
       <c r="AO62" s="56"/>
       <c r="AP62" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ62" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11981,7 +12086,9 @@
       <c r="O66" s="56">
         <v>24.7</v>
       </c>
-      <c r="P66" s="56"/>
+      <c r="P66" s="56">
+        <v>26.3</v>
+      </c>
       <c r="Q66" s="56"/>
       <c r="R66" s="56"/>
       <c r="S66" s="56"/>
@@ -12009,7 +12116,7 @@
       <c r="AO66" s="56"/>
       <c r="AP66" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ66" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12068,7 +12175,9 @@
       <c r="O67" s="56">
         <v>24.6</v>
       </c>
-      <c r="P67" s="56"/>
+      <c r="P67" s="56">
+        <v>26.1</v>
+      </c>
       <c r="Q67" s="56"/>
       <c r="R67" s="56"/>
       <c r="S67" s="56"/>
@@ -12096,7 +12205,7 @@
       <c r="AO67" s="56"/>
       <c r="AP67" s="58">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ67" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12157,7 +12266,9 @@
       <c r="O68" s="56">
         <v>23.35</v>
       </c>
-      <c r="P68" s="56"/>
+      <c r="P68" s="56">
+        <v>25.7</v>
+      </c>
       <c r="Q68" s="56"/>
       <c r="R68" s="56"/>
       <c r="S68" s="56"/>
@@ -12185,7 +12296,7 @@
       <c r="AO68" s="56"/>
       <c r="AP68" s="58">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ68" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12246,7 +12357,9 @@
       <c r="O69" s="56">
         <v>23.5</v>
       </c>
-      <c r="P69" s="56"/>
+      <c r="P69" s="56">
+        <v>25.05</v>
+      </c>
       <c r="Q69" s="56"/>
       <c r="R69" s="56"/>
       <c r="S69" s="56"/>
@@ -12274,7 +12387,7 @@
       <c r="AO69" s="56"/>
       <c r="AP69" s="58">
         <f t="shared" ref="AP69:AP132" si="3">COUNTIF(K69:AO69,"&gt;0")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ69" s="71" t="str">
         <f t="shared" ref="AQ69:AQ132" si="4">IF(AP69&gt;14,AVERAGE(K69:AO69),"")</f>
@@ -12331,7 +12444,9 @@
       <c r="O70" s="56">
         <v>25.2</v>
       </c>
-      <c r="P70" s="56"/>
+      <c r="P70" s="56">
+        <v>27.333333333333329</v>
+      </c>
       <c r="Q70" s="56"/>
       <c r="R70" s="56"/>
       <c r="S70" s="56"/>
@@ -12359,7 +12474,7 @@
       <c r="AO70" s="56"/>
       <c r="AP70" s="58">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ70" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12420,7 +12535,9 @@
       <c r="O71" s="56">
         <v>25.3</v>
       </c>
-      <c r="P71" s="56"/>
+      <c r="P71" s="56">
+        <v>26.866666666666671</v>
+      </c>
       <c r="Q71" s="56"/>
       <c r="R71" s="56"/>
       <c r="S71" s="56"/>
@@ -12448,7 +12565,7 @@
       <c r="AO71" s="56"/>
       <c r="AP71" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ71" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12509,7 +12626,9 @@
       <c r="O72" s="56">
         <v>25.93333333333333</v>
       </c>
-      <c r="P72" s="56"/>
+      <c r="P72" s="56">
+        <v>27.166666666666671</v>
+      </c>
       <c r="Q72" s="56"/>
       <c r="R72" s="56"/>
       <c r="S72" s="56"/>
@@ -12537,7 +12656,7 @@
       <c r="AO72" s="56"/>
       <c r="AP72" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ72" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12594,7 +12713,9 @@
       <c r="O73" s="56">
         <v>24</v>
       </c>
-      <c r="P73" s="56"/>
+      <c r="P73" s="56">
+        <v>25.7</v>
+      </c>
       <c r="Q73" s="56"/>
       <c r="R73" s="56"/>
       <c r="S73" s="56"/>
@@ -12622,7 +12743,7 @@
       <c r="AO73" s="56"/>
       <c r="AP73" s="58">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ73" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12683,7 +12804,9 @@
       <c r="O74" s="56">
         <v>19.25</v>
       </c>
-      <c r="P74" s="56"/>
+      <c r="P74" s="56">
+        <v>21.85</v>
+      </c>
       <c r="Q74" s="56"/>
       <c r="R74" s="56"/>
       <c r="S74" s="56"/>
@@ -12711,7 +12834,7 @@
       <c r="AO74" s="56"/>
       <c r="AP74" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ74" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12772,7 +12895,9 @@
       <c r="O75" s="56">
         <v>14.46666666666667</v>
       </c>
-      <c r="P75" s="56"/>
+      <c r="P75" s="56">
+        <v>14.93333333333333</v>
+      </c>
       <c r="Q75" s="56"/>
       <c r="R75" s="56"/>
       <c r="S75" s="56"/>
@@ -12800,7 +12925,7 @@
       <c r="AO75" s="56"/>
       <c r="AP75" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ75" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12861,7 +12986,9 @@
       <c r="O76" s="56">
         <v>19.3</v>
       </c>
-      <c r="P76" s="56"/>
+      <c r="P76" s="56">
+        <v>20.7</v>
+      </c>
       <c r="Q76" s="56"/>
       <c r="R76" s="56"/>
       <c r="S76" s="56"/>
@@ -12889,7 +13016,7 @@
       <c r="AO76" s="56"/>
       <c r="AP76" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ76" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12950,7 +13077,9 @@
       <c r="O77" s="56">
         <v>22.333333333333329</v>
       </c>
-      <c r="P77" s="56"/>
+      <c r="P77" s="56">
+        <v>25.333333333333329</v>
+      </c>
       <c r="Q77" s="56"/>
       <c r="R77" s="56"/>
       <c r="S77" s="56"/>
@@ -12978,7 +13107,7 @@
       <c r="AO77" s="56"/>
       <c r="AP77" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ77" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13039,7 +13168,9 @@
       <c r="O78" s="56">
         <v>29.9</v>
       </c>
-      <c r="P78" s="56"/>
+      <c r="P78" s="56">
+        <v>32.700000000000003</v>
+      </c>
       <c r="Q78" s="56"/>
       <c r="R78" s="56"/>
       <c r="S78" s="56"/>
@@ -13067,7 +13198,7 @@
       <c r="AO78" s="56"/>
       <c r="AP78" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ78" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13128,7 +13259,9 @@
       <c r="O79" s="56">
         <v>29.333333333333329</v>
       </c>
-      <c r="P79" s="56"/>
+      <c r="P79" s="56">
+        <v>31.6</v>
+      </c>
       <c r="Q79" s="56"/>
       <c r="R79" s="56"/>
       <c r="S79" s="56"/>
@@ -13156,7 +13289,7 @@
       <c r="AO79" s="56"/>
       <c r="AP79" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ79" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13300,7 +13433,9 @@
       <c r="O81" s="56">
         <v>23.3</v>
       </c>
-      <c r="P81" s="56"/>
+      <c r="P81" s="56">
+        <v>24.2</v>
+      </c>
       <c r="Q81" s="56"/>
       <c r="R81" s="56"/>
       <c r="S81" s="56"/>
@@ -13328,7 +13463,7 @@
       <c r="AO81" s="56"/>
       <c r="AP81" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ81" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13389,7 +13524,9 @@
       <c r="O82" s="56">
         <v>24.666666666666671</v>
       </c>
-      <c r="P82" s="56"/>
+      <c r="P82" s="56">
+        <v>25.733333333333331</v>
+      </c>
       <c r="Q82" s="56"/>
       <c r="R82" s="56"/>
       <c r="S82" s="56"/>
@@ -13417,7 +13554,7 @@
       <c r="AO82" s="56"/>
       <c r="AP82" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ82" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13636,7 +13773,9 @@
       <c r="O85" s="56">
         <v>31.35</v>
       </c>
-      <c r="P85" s="56"/>
+      <c r="P85" s="56">
+        <v>30.85</v>
+      </c>
       <c r="Q85" s="56"/>
       <c r="R85" s="56"/>
       <c r="S85" s="56"/>
@@ -13664,7 +13803,7 @@
       <c r="AO85" s="56"/>
       <c r="AP85" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ85" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13725,7 +13864,9 @@
       <c r="O86" s="56">
         <v>28.9</v>
       </c>
-      <c r="P86" s="56"/>
+      <c r="P86" s="56">
+        <v>29.25</v>
+      </c>
       <c r="Q86" s="56"/>
       <c r="R86" s="56"/>
       <c r="S86" s="56"/>
@@ -13753,7 +13894,7 @@
       <c r="AO86" s="56"/>
       <c r="AP86" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ86" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13814,7 +13955,9 @@
       <c r="O87" s="56">
         <v>31.05</v>
       </c>
-      <c r="P87" s="56"/>
+      <c r="P87" s="56">
+        <v>27.65</v>
+      </c>
       <c r="Q87" s="56"/>
       <c r="R87" s="56"/>
       <c r="S87" s="56"/>
@@ -13842,7 +13985,7 @@
       <c r="AO87" s="56"/>
       <c r="AP87" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ87" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13903,7 +14046,9 @@
       <c r="O88" s="56">
         <v>28.95</v>
       </c>
-      <c r="P88" s="56"/>
+      <c r="P88" s="56">
+        <v>27.2</v>
+      </c>
       <c r="Q88" s="56"/>
       <c r="R88" s="56"/>
       <c r="S88" s="56"/>
@@ -13931,7 +14076,7 @@
       <c r="AO88" s="56"/>
       <c r="AP88" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ88" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14079,7 +14224,9 @@
       <c r="O90" s="56">
         <v>31</v>
       </c>
-      <c r="P90" s="56"/>
+      <c r="P90" s="56">
+        <v>30.9</v>
+      </c>
       <c r="Q90" s="56"/>
       <c r="R90" s="56"/>
       <c r="S90" s="56"/>
@@ -14107,7 +14254,7 @@
       <c r="AO90" s="56"/>
       <c r="AP90" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ90" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14166,7 +14313,9 @@
       <c r="O91" s="56">
         <v>31.95</v>
       </c>
-      <c r="P91" s="56"/>
+      <c r="P91" s="56">
+        <v>29.85</v>
+      </c>
       <c r="Q91" s="56"/>
       <c r="R91" s="56"/>
       <c r="S91" s="56"/>
@@ -14194,7 +14343,7 @@
       <c r="AO91" s="56"/>
       <c r="AP91" s="58">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ91" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14255,7 +14404,9 @@
       <c r="O92" s="56">
         <v>17.100000000000001</v>
       </c>
-      <c r="P92" s="56"/>
+      <c r="P92" s="56">
+        <v>17</v>
+      </c>
       <c r="Q92" s="56"/>
       <c r="R92" s="56"/>
       <c r="S92" s="56"/>
@@ -14283,7 +14434,7 @@
       <c r="AO92" s="56"/>
       <c r="AP92" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ92" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14344,7 +14495,9 @@
       <c r="O93" s="56">
         <v>22.6</v>
       </c>
-      <c r="P93" s="56"/>
+      <c r="P93" s="56">
+        <v>22.733333333333331</v>
+      </c>
       <c r="Q93" s="56"/>
       <c r="R93" s="56"/>
       <c r="S93" s="56"/>
@@ -14372,7 +14525,7 @@
       <c r="AO93" s="56"/>
       <c r="AP93" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ93" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14433,7 +14586,9 @@
       <c r="O94" s="56">
         <v>17.45</v>
       </c>
-      <c r="P94" s="56"/>
+      <c r="P94" s="56">
+        <v>17.850000000000001</v>
+      </c>
       <c r="Q94" s="56"/>
       <c r="R94" s="56"/>
       <c r="S94" s="56"/>
@@ -14461,7 +14616,7 @@
       <c r="AO94" s="56"/>
       <c r="AP94" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ94" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14522,7 +14677,9 @@
       <c r="O95" s="56">
         <v>14.65</v>
       </c>
-      <c r="P95" s="56"/>
+      <c r="P95" s="56">
+        <v>14.7</v>
+      </c>
       <c r="Q95" s="56"/>
       <c r="R95" s="56"/>
       <c r="S95" s="56"/>
@@ -14550,7 +14707,7 @@
       <c r="AO95" s="56"/>
       <c r="AP95" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ95" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14769,7 +14926,9 @@
       <c r="O98" s="56">
         <v>13.1</v>
       </c>
-      <c r="P98" s="56"/>
+      <c r="P98" s="56">
+        <v>12.95</v>
+      </c>
       <c r="Q98" s="56"/>
       <c r="R98" s="56"/>
       <c r="S98" s="56"/>
@@ -14797,7 +14956,7 @@
       <c r="AO98" s="56"/>
       <c r="AP98" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ98" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14858,7 +15017,9 @@
       <c r="O99" s="56">
         <v>15.16666666666667</v>
       </c>
-      <c r="P99" s="56"/>
+      <c r="P99" s="56">
+        <v>14.66666666666667</v>
+      </c>
       <c r="Q99" s="56"/>
       <c r="R99" s="56"/>
       <c r="S99" s="56"/>
@@ -14886,7 +15047,7 @@
       <c r="AO99" s="56"/>
       <c r="AP99" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ99" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14947,7 +15108,9 @@
       <c r="O100" s="56">
         <v>16.2</v>
       </c>
-      <c r="P100" s="56"/>
+      <c r="P100" s="56">
+        <v>16.13333333333334</v>
+      </c>
       <c r="Q100" s="56"/>
       <c r="R100" s="56"/>
       <c r="S100" s="56"/>
@@ -14975,7 +15138,7 @@
       <c r="AO100" s="56"/>
       <c r="AP100" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ100" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15036,7 +15199,9 @@
       <c r="O101" s="56">
         <v>13.05</v>
       </c>
-      <c r="P101" s="56"/>
+      <c r="P101" s="56">
+        <v>13.35</v>
+      </c>
       <c r="Q101" s="56"/>
       <c r="R101" s="56"/>
       <c r="S101" s="56"/>
@@ -15064,7 +15229,7 @@
       <c r="AO101" s="56"/>
       <c r="AP101" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ101" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15125,7 +15290,9 @@
       <c r="O102" s="56">
         <v>12.133333333333329</v>
       </c>
-      <c r="P102" s="56"/>
+      <c r="P102" s="56">
+        <v>13</v>
+      </c>
       <c r="Q102" s="56"/>
       <c r="R102" s="56"/>
       <c r="S102" s="56"/>
@@ -15153,7 +15320,7 @@
       <c r="AO102" s="56"/>
       <c r="AP102" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ102" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15372,7 +15539,9 @@
       <c r="O105" s="56">
         <v>16.8</v>
       </c>
-      <c r="P105" s="56"/>
+      <c r="P105" s="56">
+        <v>18.2</v>
+      </c>
       <c r="Q105" s="56"/>
       <c r="R105" s="56"/>
       <c r="S105" s="56"/>
@@ -15400,7 +15569,7 @@
       <c r="AO105" s="56"/>
       <c r="AP105" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ105" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15536,7 +15705,9 @@
       <c r="O107" s="56">
         <v>13.866666666666671</v>
       </c>
-      <c r="P107" s="56"/>
+      <c r="P107" s="56">
+        <v>14.46666666666667</v>
+      </c>
       <c r="Q107" s="56"/>
       <c r="R107" s="56"/>
       <c r="S107" s="56"/>
@@ -15564,7 +15735,7 @@
       <c r="AO107" s="56"/>
       <c r="AP107" s="58">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ107" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15625,7 +15796,9 @@
       <c r="O108" s="56">
         <v>14.35</v>
       </c>
-      <c r="P108" s="56"/>
+      <c r="P108" s="56">
+        <v>14</v>
+      </c>
       <c r="Q108" s="56"/>
       <c r="R108" s="56"/>
       <c r="S108" s="56"/>
@@ -15653,7 +15826,7 @@
       <c r="AO108" s="56"/>
       <c r="AP108" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ108" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15714,7 +15887,9 @@
       <c r="O109" s="56">
         <v>13.7</v>
       </c>
-      <c r="P109" s="56"/>
+      <c r="P109" s="56">
+        <v>14.9</v>
+      </c>
       <c r="Q109" s="56"/>
       <c r="R109" s="56"/>
       <c r="S109" s="56"/>
@@ -15742,7 +15917,7 @@
       <c r="AO109" s="56"/>
       <c r="AP109" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ109" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15799,7 +15974,9 @@
       <c r="O110" s="56">
         <v>16.600000000000001</v>
       </c>
-      <c r="P110" s="56"/>
+      <c r="P110" s="56">
+        <v>16.8</v>
+      </c>
       <c r="Q110" s="56"/>
       <c r="R110" s="56"/>
       <c r="S110" s="56"/>
@@ -15827,7 +16004,7 @@
       <c r="AO110" s="56"/>
       <c r="AP110" s="58">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ110" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15888,7 +16065,9 @@
       <c r="O111" s="56">
         <v>15.4</v>
       </c>
-      <c r="P111" s="56"/>
+      <c r="P111" s="56">
+        <v>16.133333333333329</v>
+      </c>
       <c r="Q111" s="56"/>
       <c r="R111" s="56"/>
       <c r="S111" s="56"/>
@@ -15916,7 +16095,7 @@
       <c r="AO111" s="56"/>
       <c r="AP111" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ111" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15977,7 +16156,9 @@
       <c r="O112" s="56">
         <v>17.266666666666669</v>
       </c>
-      <c r="P112" s="56"/>
+      <c r="P112" s="56">
+        <v>18.2</v>
+      </c>
       <c r="Q112" s="56"/>
       <c r="R112" s="56"/>
       <c r="S112" s="56"/>
@@ -16005,7 +16186,7 @@
       <c r="AO112" s="56"/>
       <c r="AP112" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ112" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16064,7 +16245,9 @@
       <c r="O113" s="56">
         <v>18.466666666666669</v>
       </c>
-      <c r="P113" s="56"/>
+      <c r="P113" s="56">
+        <v>18.733333333333331</v>
+      </c>
       <c r="Q113" s="56"/>
       <c r="R113" s="56"/>
       <c r="S113" s="56"/>
@@ -16092,7 +16275,7 @@
       <c r="AO113" s="56"/>
       <c r="AP113" s="58">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ113" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16153,7 +16336,9 @@
       <c r="O114" s="56">
         <v>20.8</v>
       </c>
-      <c r="P114" s="56"/>
+      <c r="P114" s="56">
+        <v>21.866666666666671</v>
+      </c>
       <c r="Q114" s="56"/>
       <c r="R114" s="56"/>
       <c r="S114" s="56"/>
@@ -16181,7 +16366,7 @@
       <c r="AO114" s="56"/>
       <c r="AP114" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ114" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16242,7 +16427,9 @@
       <c r="O115" s="56">
         <v>24.4</v>
       </c>
-      <c r="P115" s="56"/>
+      <c r="P115" s="56">
+        <v>26.35</v>
+      </c>
       <c r="Q115" s="56"/>
       <c r="R115" s="56"/>
       <c r="S115" s="56"/>
@@ -16270,7 +16457,7 @@
       <c r="AO115" s="56"/>
       <c r="AP115" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ115" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16331,7 +16518,9 @@
       <c r="O116" s="56">
         <v>18.266666666666669</v>
       </c>
-      <c r="P116" s="56"/>
+      <c r="P116" s="56">
+        <v>19.86666666666666</v>
+      </c>
       <c r="Q116" s="56"/>
       <c r="R116" s="56"/>
       <c r="S116" s="56"/>
@@ -16359,7 +16548,7 @@
       <c r="AO116" s="56"/>
       <c r="AP116" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ116" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16420,7 +16609,9 @@
       <c r="O117" s="56">
         <v>24.933333333333341</v>
       </c>
-      <c r="P117" s="56"/>
+      <c r="P117" s="56">
+        <v>26.466666666666669</v>
+      </c>
       <c r="Q117" s="56"/>
       <c r="R117" s="56"/>
       <c r="S117" s="56"/>
@@ -16448,7 +16639,7 @@
       <c r="AO117" s="56"/>
       <c r="AP117" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ117" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16598,7 +16789,9 @@
       <c r="O119" s="56">
         <v>24.4</v>
       </c>
-      <c r="P119" s="56"/>
+      <c r="P119" s="56">
+        <v>23.4</v>
+      </c>
       <c r="Q119" s="56"/>
       <c r="R119" s="56"/>
       <c r="S119" s="56"/>
@@ -16626,7 +16819,7 @@
       <c r="AO119" s="56"/>
       <c r="AP119" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ119" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16682,8 +16875,12 @@
         <v>26.266666666666669</v>
       </c>
       <c r="N120" s="56"/>
-      <c r="O120" s="56"/>
-      <c r="P120" s="56"/>
+      <c r="O120" s="56">
+        <v>27.666666666666671</v>
+      </c>
+      <c r="P120" s="56">
+        <v>29.466666666666669</v>
+      </c>
       <c r="Q120" s="56"/>
       <c r="R120" s="56"/>
       <c r="S120" s="56"/>
@@ -16711,7 +16908,7 @@
       <c r="AO120" s="56"/>
       <c r="AP120" s="58">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AQ120" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16851,7 +17048,9 @@
       <c r="O122" s="56">
         <v>11.66666666666667</v>
       </c>
-      <c r="P122" s="56"/>
+      <c r="P122" s="56">
+        <v>12.06666666666667</v>
+      </c>
       <c r="Q122" s="56"/>
       <c r="R122" s="56"/>
       <c r="S122" s="56"/>
@@ -16879,7 +17078,7 @@
       <c r="AO122" s="56"/>
       <c r="AP122" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ122" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17179,7 +17378,9 @@
         <v>11.33333333333333</v>
       </c>
       <c r="O126" s="56"/>
-      <c r="P126" s="56"/>
+      <c r="P126" s="56">
+        <v>10.733333333333331</v>
+      </c>
       <c r="Q126" s="56"/>
       <c r="R126" s="56"/>
       <c r="S126" s="56"/>
@@ -17207,7 +17408,7 @@
       <c r="AO126" s="56"/>
       <c r="AP126" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ126" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17499,9 +17700,15 @@
       <c r="M130" s="56">
         <v>15.43333333333333</v>
       </c>
-      <c r="N130" s="56"/>
-      <c r="O130" s="56"/>
-      <c r="P130" s="56"/>
+      <c r="N130" s="56">
+        <v>14.53333333333333</v>
+      </c>
+      <c r="O130" s="56">
+        <v>13.766666666666669</v>
+      </c>
+      <c r="P130" s="56">
+        <v>15.133333333333329</v>
+      </c>
       <c r="Q130" s="56"/>
       <c r="R130" s="56"/>
       <c r="S130" s="56"/>
@@ -17529,7 +17736,7 @@
       <c r="AO130" s="56"/>
       <c r="AP130" s="58">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AQ130" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17590,7 +17797,9 @@
       <c r="O131" s="56">
         <v>17.45</v>
       </c>
-      <c r="P131" s="56"/>
+      <c r="P131" s="56">
+        <v>17.05</v>
+      </c>
       <c r="Q131" s="56"/>
       <c r="R131" s="56"/>
       <c r="S131" s="56"/>
@@ -17618,7 +17827,7 @@
       <c r="AO131" s="56"/>
       <c r="AP131" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ131" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17758,7 +17967,9 @@
       <c r="O133" s="56">
         <v>13.46666666666667</v>
       </c>
-      <c r="P133" s="56"/>
+      <c r="P133" s="56">
+        <v>11.93333333333333</v>
+      </c>
       <c r="Q133" s="56"/>
       <c r="R133" s="56"/>
       <c r="S133" s="56"/>
@@ -17786,7 +17997,7 @@
       <c r="AO133" s="56"/>
       <c r="AP133" s="58">
         <f t="shared" ref="AP133:AP196" si="6">COUNTIF(K133:AO133,"&gt;0")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ133" s="71" t="str">
         <f t="shared" ref="AQ133:AQ196" si="7">IF(AP133&gt;14,AVERAGE(K133:AO133),"")</f>
@@ -17844,8 +18055,12 @@
       <c r="N134" s="56">
         <v>17</v>
       </c>
-      <c r="O134" s="56"/>
-      <c r="P134" s="56"/>
+      <c r="O134" s="56">
+        <v>17.2</v>
+      </c>
+      <c r="P134" s="56">
+        <v>17.600000000000001</v>
+      </c>
       <c r="Q134" s="56"/>
       <c r="R134" s="56"/>
       <c r="S134" s="56"/>
@@ -17873,7 +18088,7 @@
       <c r="AO134" s="56"/>
       <c r="AP134" s="58">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AQ134" s="71" t="str">
         <f t="shared" si="7"/>
@@ -17934,7 +18149,9 @@
       <c r="O135" s="56">
         <v>20.55</v>
       </c>
-      <c r="P135" s="56"/>
+      <c r="P135" s="56">
+        <v>18.925000000000001</v>
+      </c>
       <c r="Q135" s="56"/>
       <c r="R135" s="56"/>
       <c r="S135" s="56"/>
@@ -17962,7 +18179,7 @@
       <c r="AO135" s="56"/>
       <c r="AP135" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ135" s="71" t="str">
         <f t="shared" si="7"/>
@@ -18191,7 +18408,9 @@
       <c r="O138" s="56">
         <v>22.93333333333333</v>
       </c>
-      <c r="P138" s="56"/>
+      <c r="P138" s="56">
+        <v>21.333333333333329</v>
+      </c>
       <c r="Q138" s="56"/>
       <c r="R138" s="56"/>
       <c r="S138" s="56"/>
@@ -18219,7 +18438,7 @@
       <c r="AO138" s="56"/>
       <c r="AP138" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ138" s="71" t="str">
         <f t="shared" si="7"/>
@@ -18280,7 +18499,9 @@
       <c r="O139" s="56">
         <v>12.5</v>
       </c>
-      <c r="P139" s="56"/>
+      <c r="P139" s="56">
+        <v>13.05</v>
+      </c>
       <c r="Q139" s="56"/>
       <c r="R139" s="56"/>
       <c r="S139" s="56"/>
@@ -18308,7 +18529,7 @@
       <c r="AO139" s="56"/>
       <c r="AP139" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ139" s="71" t="str">
         <f t="shared" si="7"/>
@@ -18369,7 +18590,9 @@
       <c r="O140" s="56">
         <v>15.55</v>
       </c>
-      <c r="P140" s="56"/>
+      <c r="P140" s="56">
+        <v>15.7</v>
+      </c>
       <c r="Q140" s="56"/>
       <c r="R140" s="56"/>
       <c r="S140" s="56"/>
@@ -18397,7 +18620,7 @@
       <c r="AO140" s="56"/>
       <c r="AP140" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ140" s="71" t="str">
         <f t="shared" si="7"/>
@@ -18458,7 +18681,9 @@
       <c r="O141" s="56">
         <v>13</v>
       </c>
-      <c r="P141" s="56"/>
+      <c r="P141" s="56">
+        <v>12</v>
+      </c>
       <c r="Q141" s="56"/>
       <c r="R141" s="56"/>
       <c r="S141" s="56"/>
@@ -18486,7 +18711,7 @@
       <c r="AO141" s="56"/>
       <c r="AP141" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ141" s="71" t="str">
         <f t="shared" si="7"/>
@@ -18636,7 +18861,9 @@
       <c r="O143" s="56">
         <v>26.466666666666669</v>
       </c>
-      <c r="P143" s="56"/>
+      <c r="P143" s="56">
+        <v>25.86666666666666</v>
+      </c>
       <c r="Q143" s="56"/>
       <c r="R143" s="56"/>
       <c r="S143" s="56"/>
@@ -18664,7 +18891,7 @@
       <c r="AO143" s="56"/>
       <c r="AP143" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ143" s="71" t="str">
         <f t="shared" si="7"/>
@@ -18814,7 +19041,9 @@
       <c r="O145" s="56">
         <v>21.466666666666669</v>
       </c>
-      <c r="P145" s="56"/>
+      <c r="P145" s="56">
+        <v>19.06666666666667</v>
+      </c>
       <c r="Q145" s="56"/>
       <c r="R145" s="56"/>
       <c r="S145" s="56"/>
@@ -18842,7 +19071,7 @@
       <c r="AO145" s="56"/>
       <c r="AP145" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ145" s="71" t="str">
         <f t="shared" si="7"/>
@@ -18888,16 +19117,24 @@
       <c r="J146" s="60" t="s">
         <v>308</v>
       </c>
-      <c r="K146" s="56"/>
-      <c r="L146" s="56"/>
+      <c r="K146" s="56">
+        <v>32.93333333333333</v>
+      </c>
+      <c r="L146" s="56">
+        <v>32.466666666666669</v>
+      </c>
       <c r="M146" s="56">
         <v>31.6</v>
       </c>
       <c r="N146" s="56">
         <v>31.333333333333329</v>
       </c>
-      <c r="O146" s="56"/>
-      <c r="P146" s="56"/>
+      <c r="O146" s="56">
+        <v>29.533333333333331</v>
+      </c>
+      <c r="P146" s="56">
+        <v>30.13333333333334</v>
+      </c>
       <c r="Q146" s="56"/>
       <c r="R146" s="56"/>
       <c r="S146" s="56"/>
@@ -18925,7 +19162,7 @@
       <c r="AO146" s="56"/>
       <c r="AP146" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AQ146" s="71" t="str">
         <f t="shared" si="7"/>
@@ -18986,7 +19223,9 @@
       <c r="O147" s="56">
         <v>25.666666666666671</v>
       </c>
-      <c r="P147" s="56"/>
+      <c r="P147" s="56">
+        <v>26.066666666666659</v>
+      </c>
       <c r="Q147" s="56"/>
       <c r="R147" s="56"/>
       <c r="S147" s="56"/>
@@ -19014,7 +19253,7 @@
       <c r="AO147" s="56"/>
       <c r="AP147" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ147" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19164,7 +19403,9 @@
       <c r="O149" s="56">
         <v>24.066666666666659</v>
       </c>
-      <c r="P149" s="56"/>
+      <c r="P149" s="56">
+        <v>23.666666666666671</v>
+      </c>
       <c r="Q149" s="56"/>
       <c r="R149" s="56"/>
       <c r="S149" s="56"/>
@@ -19192,7 +19433,7 @@
       <c r="AO149" s="56"/>
       <c r="AP149" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ149" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19317,8 +19558,12 @@
       <c r="J151" s="60" t="s">
         <v>315</v>
       </c>
-      <c r="K151" s="56"/>
-      <c r="L151" s="56"/>
+      <c r="K151" s="56">
+        <v>25.86666666666666</v>
+      </c>
+      <c r="L151" s="56">
+        <v>24.6</v>
+      </c>
       <c r="M151" s="56">
         <v>23.8</v>
       </c>
@@ -19356,7 +19601,7 @@
       <c r="AO151" s="56"/>
       <c r="AP151" s="58">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AQ151" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19575,7 +19820,9 @@
       <c r="O154" s="56">
         <v>20.5</v>
       </c>
-      <c r="P154" s="56"/>
+      <c r="P154" s="56">
+        <v>20.5</v>
+      </c>
       <c r="Q154" s="56"/>
       <c r="R154" s="56"/>
       <c r="S154" s="56"/>
@@ -19603,7 +19850,7 @@
       <c r="AO154" s="56"/>
       <c r="AP154" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ154" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19662,7 +19909,9 @@
       <c r="O155" s="56">
         <v>28.933333333333341</v>
       </c>
-      <c r="P155" s="56"/>
+      <c r="P155" s="56">
+        <v>27.93333333333333</v>
+      </c>
       <c r="Q155" s="56"/>
       <c r="R155" s="56"/>
       <c r="S155" s="56"/>
@@ -19690,7 +19939,7 @@
       <c r="AO155" s="56"/>
       <c r="AP155" s="58">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ155" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19815,8 +20064,12 @@
       <c r="J157" s="60" t="s">
         <v>45</v>
       </c>
-      <c r="K157" s="56"/>
-      <c r="L157" s="56"/>
+      <c r="K157" s="56">
+        <v>30.466666666666669</v>
+      </c>
+      <c r="L157" s="56">
+        <v>30.6</v>
+      </c>
       <c r="M157" s="56">
         <v>30.06666666666667</v>
       </c>
@@ -19826,7 +20079,9 @@
       <c r="O157" s="56">
         <v>30.533333333333331</v>
       </c>
-      <c r="P157" s="56"/>
+      <c r="P157" s="56">
+        <v>29</v>
+      </c>
       <c r="Q157" s="56"/>
       <c r="R157" s="56"/>
       <c r="S157" s="56"/>
@@ -19854,7 +20109,7 @@
       <c r="AO157" s="56"/>
       <c r="AP157" s="58">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AQ157" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19915,7 +20170,9 @@
       <c r="O158" s="56">
         <v>29.533333333333331</v>
       </c>
-      <c r="P158" s="56"/>
+      <c r="P158" s="56">
+        <v>27.6</v>
+      </c>
       <c r="Q158" s="56"/>
       <c r="R158" s="56"/>
       <c r="S158" s="56"/>
@@ -19943,7 +20200,7 @@
       <c r="AO158" s="56"/>
       <c r="AP158" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ158" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20004,7 +20261,9 @@
       <c r="O159" s="56">
         <v>19.600000000000001</v>
       </c>
-      <c r="P159" s="56"/>
+      <c r="P159" s="56">
+        <v>20.399999999999999</v>
+      </c>
       <c r="Q159" s="56"/>
       <c r="R159" s="56"/>
       <c r="S159" s="56"/>
@@ -20032,7 +20291,7 @@
       <c r="AO159" s="56"/>
       <c r="AP159" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ159" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20091,7 +20350,9 @@
       <c r="O160" s="56">
         <v>28.06666666666667</v>
       </c>
-      <c r="P160" s="56"/>
+      <c r="P160" s="56">
+        <v>24.466666666666669</v>
+      </c>
       <c r="Q160" s="56"/>
       <c r="R160" s="56"/>
       <c r="S160" s="56"/>
@@ -20119,7 +20380,7 @@
       <c r="AO160" s="56"/>
       <c r="AP160" s="58">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ160" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20177,8 +20438,12 @@
       <c r="N161" s="56">
         <v>19</v>
       </c>
-      <c r="O161" s="56"/>
-      <c r="P161" s="56"/>
+      <c r="O161" s="56">
+        <v>20.266666666666669</v>
+      </c>
+      <c r="P161" s="56">
+        <v>18.666666666666671</v>
+      </c>
       <c r="Q161" s="56"/>
       <c r="R161" s="56"/>
       <c r="S161" s="56"/>
@@ -20206,7 +20471,7 @@
       <c r="AO161" s="56"/>
       <c r="AP161" s="58">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AQ161" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20267,7 +20532,9 @@
       <c r="O162" s="56">
         <v>28</v>
       </c>
-      <c r="P162" s="56"/>
+      <c r="P162" s="56">
+        <v>28.266666666666669</v>
+      </c>
       <c r="Q162" s="56"/>
       <c r="R162" s="56"/>
       <c r="S162" s="56"/>
@@ -20295,7 +20562,7 @@
       <c r="AO162" s="56"/>
       <c r="AP162" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ162" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20356,7 +20623,9 @@
       <c r="O163" s="56">
         <v>22.06666666666667</v>
       </c>
-      <c r="P163" s="56"/>
+      <c r="P163" s="56">
+        <v>21.466666666666669</v>
+      </c>
       <c r="Q163" s="56"/>
       <c r="R163" s="56"/>
       <c r="S163" s="56"/>
@@ -20384,7 +20653,7 @@
       <c r="AO163" s="56"/>
       <c r="AP163" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ163" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20433,15 +20702,21 @@
       <c r="K164" s="56">
         <v>26.35</v>
       </c>
-      <c r="L164" s="56"/>
-      <c r="M164" s="56"/>
+      <c r="L164" s="56">
+        <v>26.1</v>
+      </c>
+      <c r="M164" s="56">
+        <v>25.7</v>
+      </c>
       <c r="N164" s="56">
         <v>23.9</v>
       </c>
       <c r="O164" s="56">
         <v>26.25</v>
       </c>
-      <c r="P164" s="56"/>
+      <c r="P164" s="56">
+        <v>25.25</v>
+      </c>
       <c r="Q164" s="56"/>
       <c r="R164" s="56"/>
       <c r="S164" s="56"/>
@@ -20469,7 +20744,7 @@
       <c r="AO164" s="56"/>
       <c r="AP164" s="58">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AQ164" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20609,7 +20884,9 @@
       <c r="O166" s="56">
         <v>14.8</v>
       </c>
-      <c r="P166" s="56"/>
+      <c r="P166" s="56">
+        <v>14.2</v>
+      </c>
       <c r="Q166" s="56"/>
       <c r="R166" s="56"/>
       <c r="S166" s="56"/>
@@ -20637,7 +20914,7 @@
       <c r="AO166" s="56"/>
       <c r="AP166" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ166" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20694,7 +20971,9 @@
       </c>
       <c r="N167" s="56"/>
       <c r="O167" s="56"/>
-      <c r="P167" s="56"/>
+      <c r="P167" s="56">
+        <v>19.733333333333331</v>
+      </c>
       <c r="Q167" s="56"/>
       <c r="R167" s="56"/>
       <c r="S167" s="56"/>
@@ -20722,7 +21001,7 @@
       <c r="AO167" s="56"/>
       <c r="AP167" s="58">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ167" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20783,7 +21062,9 @@
       <c r="O168" s="56">
         <v>27.65</v>
       </c>
-      <c r="P168" s="56"/>
+      <c r="P168" s="56">
+        <v>26.45</v>
+      </c>
       <c r="Q168" s="56"/>
       <c r="R168" s="56"/>
       <c r="S168" s="56"/>
@@ -20811,7 +21092,7 @@
       <c r="AO168" s="56"/>
       <c r="AP168" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ168" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20872,7 +21153,9 @@
       <c r="O169" s="56">
         <v>8.3000000000000007</v>
       </c>
-      <c r="P169" s="56"/>
+      <c r="P169" s="56">
+        <v>9</v>
+      </c>
       <c r="Q169" s="56"/>
       <c r="R169" s="56"/>
       <c r="S169" s="56"/>
@@ -20900,7 +21183,7 @@
       <c r="AO169" s="56"/>
       <c r="AP169" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ169" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20961,7 +21244,9 @@
       <c r="O170" s="56">
         <v>26</v>
       </c>
-      <c r="P170" s="56"/>
+      <c r="P170" s="56">
+        <v>24.8</v>
+      </c>
       <c r="Q170" s="56"/>
       <c r="R170" s="56"/>
       <c r="S170" s="56"/>
@@ -20989,7 +21274,7 @@
       <c r="AO170" s="56"/>
       <c r="AP170" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ170" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21137,7 +21422,9 @@
       <c r="O172" s="56">
         <v>24.65</v>
       </c>
-      <c r="P172" s="56"/>
+      <c r="P172" s="56">
+        <v>25.05</v>
+      </c>
       <c r="Q172" s="56"/>
       <c r="R172" s="56"/>
       <c r="S172" s="56"/>
@@ -21165,7 +21452,7 @@
       <c r="AO172" s="56"/>
       <c r="AP172" s="58">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ172" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21226,7 +21513,9 @@
       <c r="O173" s="56">
         <v>24.6</v>
       </c>
-      <c r="P173" s="56"/>
+      <c r="P173" s="56">
+        <v>24.95</v>
+      </c>
       <c r="Q173" s="56"/>
       <c r="R173" s="56"/>
       <c r="S173" s="56"/>
@@ -21254,7 +21543,7 @@
       <c r="AO173" s="56"/>
       <c r="AP173" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ173" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21398,7 +21687,9 @@
       <c r="M175" s="56"/>
       <c r="N175" s="56"/>
       <c r="O175" s="56"/>
-      <c r="P175" s="56"/>
+      <c r="P175" s="56">
+        <v>25.86666666666666</v>
+      </c>
       <c r="Q175" s="56"/>
       <c r="R175" s="56"/>
       <c r="S175" s="56"/>
@@ -21426,7 +21717,7 @@
       <c r="AO175" s="56"/>
       <c r="AP175" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ175" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21645,7 +21936,9 @@
       <c r="O178" s="56">
         <v>25.4</v>
       </c>
-      <c r="P178" s="56"/>
+      <c r="P178" s="56">
+        <v>24.466666666666669</v>
+      </c>
       <c r="Q178" s="56"/>
       <c r="R178" s="56"/>
       <c r="S178" s="56"/>
@@ -21673,7 +21966,7 @@
       <c r="AO178" s="56"/>
       <c r="AP178" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ178" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21734,7 +22027,9 @@
       <c r="O179" s="56">
         <v>19.100000000000001</v>
       </c>
-      <c r="P179" s="56"/>
+      <c r="P179" s="56">
+        <v>17.25</v>
+      </c>
       <c r="Q179" s="56"/>
       <c r="R179" s="56"/>
       <c r="S179" s="56"/>
@@ -21762,7 +22057,7 @@
       <c r="AO179" s="56"/>
       <c r="AP179" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ179" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21902,7 +22197,9 @@
       <c r="O181" s="56">
         <v>29.133333333333329</v>
       </c>
-      <c r="P181" s="56"/>
+      <c r="P181" s="56">
+        <v>32.799999999999997</v>
+      </c>
       <c r="Q181" s="56"/>
       <c r="R181" s="56"/>
       <c r="S181" s="56"/>
@@ -21930,7 +22227,7 @@
       <c r="AO181" s="56"/>
       <c r="AP181" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ181" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22149,7 +22446,9 @@
       <c r="O184" s="56">
         <v>26.13333333333334</v>
       </c>
-      <c r="P184" s="56"/>
+      <c r="P184" s="56">
+        <v>29.533333333333331</v>
+      </c>
       <c r="Q184" s="56"/>
       <c r="R184" s="56"/>
       <c r="S184" s="56"/>
@@ -22177,7 +22476,7 @@
       <c r="AO184" s="56"/>
       <c r="AP184" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ184" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22483,7 +22782,9 @@
       <c r="O188" s="56">
         <v>16.399999999999999</v>
       </c>
-      <c r="P188" s="56"/>
+      <c r="P188" s="56">
+        <v>17.2</v>
+      </c>
       <c r="Q188" s="56"/>
       <c r="R188" s="56"/>
       <c r="S188" s="56"/>
@@ -22511,7 +22812,7 @@
       <c r="AO188" s="56"/>
       <c r="AP188" s="58">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ188" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22659,7 +22960,9 @@
       <c r="O190" s="56">
         <v>28.4</v>
       </c>
-      <c r="P190" s="56"/>
+      <c r="P190" s="56">
+        <v>29.4</v>
+      </c>
       <c r="Q190" s="56"/>
       <c r="R190" s="56"/>
       <c r="S190" s="56"/>
@@ -22687,7 +22990,7 @@
       <c r="AO190" s="56"/>
       <c r="AP190" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ190" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22748,7 +23051,9 @@
       <c r="O191" s="56">
         <v>17.75</v>
       </c>
-      <c r="P191" s="56"/>
+      <c r="P191" s="56">
+        <v>18.25</v>
+      </c>
       <c r="Q191" s="56"/>
       <c r="R191" s="56"/>
       <c r="S191" s="56"/>
@@ -22776,7 +23081,7 @@
       <c r="AO191" s="56"/>
       <c r="AP191" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ191" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22837,7 +23142,9 @@
       <c r="O192" s="56">
         <v>25.13333333333334</v>
       </c>
-      <c r="P192" s="56"/>
+      <c r="P192" s="56">
+        <v>24.466666666666669</v>
+      </c>
       <c r="Q192" s="56"/>
       <c r="R192" s="56"/>
       <c r="S192" s="56"/>
@@ -22865,7 +23172,7 @@
       <c r="AO192" s="56"/>
       <c r="AP192" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ192" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22926,7 +23233,9 @@
       <c r="O193" s="56">
         <v>25.35</v>
       </c>
-      <c r="P193" s="56"/>
+      <c r="P193" s="56">
+        <v>28.15</v>
+      </c>
       <c r="Q193" s="56"/>
       <c r="R193" s="56"/>
       <c r="S193" s="56"/>
@@ -22954,7 +23263,7 @@
       <c r="AO193" s="56"/>
       <c r="AP193" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ193" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23104,7 +23413,9 @@
       <c r="O195" s="56">
         <v>25.13333333333334</v>
       </c>
-      <c r="P195" s="56"/>
+      <c r="P195" s="56">
+        <v>26.266666666666669</v>
+      </c>
       <c r="Q195" s="56"/>
       <c r="R195" s="56"/>
       <c r="S195" s="56"/>
@@ -23132,7 +23443,7 @@
       <c r="AO195" s="56"/>
       <c r="AP195" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ195" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23193,7 +23504,9 @@
       <c r="O196" s="56">
         <v>20.533333333333331</v>
       </c>
-      <c r="P196" s="56"/>
+      <c r="P196" s="56">
+        <v>20.333333333333329</v>
+      </c>
       <c r="Q196" s="56"/>
       <c r="R196" s="56"/>
       <c r="S196" s="56"/>
@@ -23221,7 +23534,7 @@
       <c r="AO196" s="56"/>
       <c r="AP196" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ196" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23282,7 +23595,9 @@
       <c r="O197" s="56">
         <v>25.2</v>
       </c>
-      <c r="P197" s="56"/>
+      <c r="P197" s="56">
+        <v>26.533333333333331</v>
+      </c>
       <c r="Q197" s="56"/>
       <c r="R197" s="56"/>
       <c r="S197" s="56"/>
@@ -23309,11 +23624,11 @@
       <c r="AN197" s="56"/>
       <c r="AO197" s="56"/>
       <c r="AP197" s="58">
-        <f t="shared" ref="AP197:AP260" si="9">COUNTIF(K197:AO197,"&gt;0")</f>
-        <v>5</v>
+        <f t="shared" ref="AP197:AP212" si="9">COUNTIF(K197:AO197,"&gt;0")</f>
+        <v>6</v>
       </c>
       <c r="AQ197" s="71" t="str">
-        <f t="shared" ref="AQ197:AQ260" si="10">IF(AP197&gt;14,AVERAGE(K197:AO197),"")</f>
+        <f t="shared" ref="AQ197:AQ212" si="10">IF(AP197&gt;14,AVERAGE(K197:AO197),"")</f>
         <v/>
       </c>
       <c r="AR197" s="71">
@@ -23321,7 +23636,7 @@
         <v>24.669620158482161</v>
       </c>
       <c r="AS197" s="71" t="str">
-        <f t="shared" ref="AS197:AS260" si="11">IF(OR(AQ197="",AR197=""),"",IFERROR(AQ197-AR197,""))</f>
+        <f t="shared" ref="AS197:AS212" si="11">IF(OR(AQ197="",AR197=""),"",IFERROR(AQ197-AR197,""))</f>
         <v/>
       </c>
     </row>
@@ -23371,7 +23686,9 @@
       <c r="O198" s="56">
         <v>20.9</v>
       </c>
-      <c r="P198" s="56"/>
+      <c r="P198" s="56">
+        <v>22.15</v>
+      </c>
       <c r="Q198" s="56"/>
       <c r="R198" s="56"/>
       <c r="S198" s="56"/>
@@ -23399,7 +23716,7 @@
       <c r="AO198" s="56"/>
       <c r="AP198" s="58">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ198" s="71" t="str">
         <f t="shared" si="10"/>
@@ -23460,7 +23777,9 @@
       <c r="O199" s="56">
         <v>16.600000000000001</v>
       </c>
-      <c r="P199" s="56"/>
+      <c r="P199" s="56">
+        <v>17</v>
+      </c>
       <c r="Q199" s="56"/>
       <c r="R199" s="56"/>
       <c r="S199" s="56"/>
@@ -23488,7 +23807,7 @@
       <c r="AO199" s="56"/>
       <c r="AP199" s="58">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ199" s="71" t="str">
         <f t="shared" si="10"/>
@@ -23549,7 +23868,9 @@
       <c r="O200" s="56">
         <v>14.7</v>
       </c>
-      <c r="P200" s="56"/>
+      <c r="P200" s="56">
+        <v>14.95</v>
+      </c>
       <c r="Q200" s="56"/>
       <c r="R200" s="56"/>
       <c r="S200" s="56"/>
@@ -23577,7 +23898,7 @@
       <c r="AO200" s="56"/>
       <c r="AP200" s="58">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ200" s="71" t="str">
         <f t="shared" si="10"/>
@@ -23638,7 +23959,9 @@
       <c r="O201" s="56">
         <v>26.4</v>
       </c>
-      <c r="P201" s="56"/>
+      <c r="P201" s="56">
+        <v>27.95</v>
+      </c>
       <c r="Q201" s="56"/>
       <c r="R201" s="56"/>
       <c r="S201" s="56"/>
@@ -23666,7 +23989,7 @@
       <c r="AO201" s="56"/>
       <c r="AP201" s="58">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ201" s="71" t="str">
         <f t="shared" si="10"/>
@@ -23727,7 +24050,9 @@
       <c r="O202" s="56">
         <v>12.2</v>
       </c>
-      <c r="P202" s="56"/>
+      <c r="P202" s="56">
+        <v>12.2</v>
+      </c>
       <c r="Q202" s="56"/>
       <c r="R202" s="56"/>
       <c r="S202" s="56"/>
@@ -23755,7 +24080,7 @@
       <c r="AO202" s="56"/>
       <c r="AP202" s="58">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ202" s="71" t="str">
         <f t="shared" si="10"/>
@@ -23984,7 +24309,9 @@
       <c r="O205" s="56">
         <v>13</v>
       </c>
-      <c r="P205" s="56"/>
+      <c r="P205" s="56">
+        <v>11.9</v>
+      </c>
       <c r="Q205" s="56"/>
       <c r="R205" s="56"/>
       <c r="S205" s="56"/>
@@ -24012,7 +24339,7 @@
       <c r="AO205" s="56"/>
       <c r="AP205" s="58">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ205" s="71" t="str">
         <f t="shared" si="10"/>
@@ -24073,7 +24400,9 @@
       <c r="O206" s="56">
         <v>13.35</v>
       </c>
-      <c r="P206" s="56"/>
+      <c r="P206" s="56">
+        <v>12.75</v>
+      </c>
       <c r="Q206" s="56"/>
       <c r="R206" s="56"/>
       <c r="S206" s="56"/>
@@ -24101,7 +24430,7 @@
       <c r="AO206" s="56"/>
       <c r="AP206" s="58">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ206" s="71" t="str">
         <f t="shared" si="10"/>
@@ -24247,7 +24576,9 @@
       <c r="O208" s="56">
         <v>13.2</v>
       </c>
-      <c r="P208" s="56"/>
+      <c r="P208" s="56">
+        <v>12.85</v>
+      </c>
       <c r="Q208" s="56"/>
       <c r="R208" s="56"/>
       <c r="S208" s="56"/>
@@ -24275,7 +24606,7 @@
       <c r="AO208" s="56"/>
       <c r="AP208" s="58">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ208" s="71" t="str">
         <f t="shared" si="10"/>
@@ -24336,7 +24667,9 @@
       <c r="O209" s="56">
         <v>11.4</v>
       </c>
-      <c r="P209" s="56"/>
+      <c r="P209" s="56">
+        <v>11.1</v>
+      </c>
       <c r="Q209" s="56"/>
       <c r="R209" s="56"/>
       <c r="S209" s="56"/>
@@ -24364,7 +24697,7 @@
       <c r="AO209" s="56"/>
       <c r="AP209" s="58">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ209" s="71" t="str">
         <f t="shared" si="10"/>
@@ -24425,7 +24758,9 @@
       <c r="O210" s="56">
         <v>15.35</v>
       </c>
-      <c r="P210" s="56"/>
+      <c r="P210" s="56">
+        <v>17.05</v>
+      </c>
       <c r="Q210" s="56"/>
       <c r="R210" s="56"/>
       <c r="S210" s="56"/>
@@ -24453,7 +24788,7 @@
       <c r="AO210" s="56"/>
       <c r="AP210" s="58">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ210" s="71" t="str">
         <f t="shared" si="10"/>
@@ -24512,9 +24847,11 @@
         <v>6.9</v>
       </c>
       <c r="O211" s="56">
-        <v>7.5</v>
-      </c>
-      <c r="P211" s="56"/>
+        <v>7.7</v>
+      </c>
+      <c r="P211" s="56">
+        <v>7.9499999999999993</v>
+      </c>
       <c r="Q211" s="56"/>
       <c r="R211" s="56"/>
       <c r="S211" s="56"/>
@@ -24542,7 +24879,7 @@
       <c r="AO211" s="56"/>
       <c r="AP211" s="58">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ211" s="71" t="str">
         <f t="shared" si="10"/>
@@ -24598,7 +24935,9 @@
       <c r="N212" s="56">
         <v>27.7</v>
       </c>
-      <c r="O212" s="56"/>
+      <c r="O212" s="56">
+        <v>27.75</v>
+      </c>
       <c r="P212" s="56"/>
       <c r="Q212" s="56"/>
       <c r="R212" s="56"/>
@@ -24627,7 +24966,7 @@
       <c r="AO212" s="56"/>
       <c r="AP212" s="58">
         <f t="shared" si="9"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ212" s="71" t="str">
         <f t="shared" si="10"/>
